--- a/data/trans_orig/IP24_R2_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP24_R2_2023-Estudios-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>11486</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>7009</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>16998</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>20,59%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>12,57%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>30,48%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>16888</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>9587</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>30478</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>30,89%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>17,53%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>55,74%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>13928</t>
+          <t>9060</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>8679</t>
+          <t>5441</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>20357</t>
+          <t>14056</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>22,81%</t>
+          <t>19,38%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>14,21%</t>
+          <t>11,64%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>33,33%</t>
+          <t>30,06%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>30816</t>
+          <t>20546</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>21483</t>
+          <t>14500</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>45587</t>
+          <t>27480</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>26,62%</t>
+          <t>20,04%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>18,56%</t>
+          <t>14,14%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>39,39%</t>
+          <t>26,8%</t>
         </is>
       </c>
     </row>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>44284</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>38772</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>48761</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>79,41%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>69,52%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>87,43%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>53</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>37790</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>24200</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>45091</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>69,11%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>44,26%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>82,47%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>47139</t>
+          <t>37698</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>40710</t>
+          <t>32702</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>52388</t>
+          <t>41317</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>77,19%</t>
+          <t>80,62%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>66,67%</t>
+          <t>69,94%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>85,79%</t>
+          <t>88,36%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>84928</t>
+          <t>81982</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>70157</t>
+          <t>75048</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>94261</t>
+          <t>88028</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>73,38%</t>
+          <t>79,96%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>60,61%</t>
+          <t>73,2%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>81,44%</t>
+          <t>85,86%</t>
         </is>
       </c>
     </row>
@@ -946,57 +946,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>55770</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>55770</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>55770</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>69</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>54678</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>54678</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>54678</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>61067</t>
+          <t>46758</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>61067</t>
+          <t>46758</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>61067</t>
+          <t>46758</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>115744</t>
+          <t>102528</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>115744</t>
+          <t>102528</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>115744</t>
+          <t>102528</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1063,72 +1063,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>125</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>78081</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>63214</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>103692</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>16,48%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>13,35%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>21,89%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>129</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>112812</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>85871</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>176869</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>24,62%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>18,74%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>38,6%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>125</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>91962</t>
+          <t>79352</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>75371</t>
+          <t>67058</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>124536</t>
+          <t>94967</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>17,89%</t>
+          <t>18,44%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>14,66%</t>
+          <t>15,58%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>24,23%</t>
+          <t>22,07%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>204774</t>
+          <t>157433</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>169247</t>
+          <t>138049</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>271527</t>
+          <t>184852</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>21,06%</t>
+          <t>17,42%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>17,41%</t>
+          <t>15,27%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>27,93%</t>
+          <t>20,45%</t>
         </is>
       </c>
     </row>
@@ -1176,72 +1176,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>525</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>395603</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>369992</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>410470</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>83,52%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>78,11%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>86,65%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>510</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>345371</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>281314</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>372312</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>75,38%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>61,4%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>81,26%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>525</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>422085</t>
+          <t>350939</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>389511</t>
+          <t>335324</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>438676</t>
+          <t>363233</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>82,11%</t>
+          <t>81,56%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>75,77%</t>
+          <t>77,93%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>85,34%</t>
+          <t>84,42%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>767457</t>
+          <t>746542</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>700704</t>
+          <t>719123</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>802984</t>
+          <t>765926</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>78,94%</t>
+          <t>82,58%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>72,07%</t>
+          <t>79,55%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>82,59%</t>
+          <t>84,73%</t>
         </is>
       </c>
     </row>
@@ -1289,57 +1289,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>650</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>473684</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>473684</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>473684</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>639</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>458183</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>458183</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>458183</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>650</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>514047</t>
+          <t>430291</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>514047</t>
+          <t>430291</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>514047</t>
+          <t>430291</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>972231</t>
+          <t>903975</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>972231</t>
+          <t>903975</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>972231</t>
+          <t>903975</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1406,72 +1406,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>25778</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>18378</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>34929</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>15,36%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>10,95%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>20,82%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>40</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>25695</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>18460</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>34545</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>17,18%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>12,34%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>23,1%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>29610</t>
+          <t>23674</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>21715</t>
+          <t>17446</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>39336</t>
+          <t>31945</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>16,22%</t>
+          <t>15,79%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11,89%</t>
+          <t>11,63%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>21,54%</t>
+          <t>21,3%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>55306</t>
+          <t>49452</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>44611</t>
+          <t>40216</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>67025</t>
+          <t>61273</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>16,65%</t>
+          <t>15,56%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>13,43%</t>
+          <t>12,66%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>20,18%</t>
+          <t>19,28%</t>
         </is>
       </c>
     </row>
@@ -1519,72 +1519,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>196</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>141997</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>132846</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>149397</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>84,64%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>79,18%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>89,05%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>190</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>123856</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>115006</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>131091</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>82,82%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>76,9%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>87,66%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>196</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>152973</t>
+          <t>126302</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>143247</t>
+          <t>118031</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>160868</t>
+          <t>132530</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>83,78%</t>
+          <t>84,21%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>78,46%</t>
+          <t>78,7%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>88,11%</t>
+          <t>88,37%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>276828</t>
+          <t>268299</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>265109</t>
+          <t>256478</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>287523</t>
+          <t>277535</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>83,35%</t>
+          <t>84,44%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>79,82%</t>
+          <t>80,72%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>86,57%</t>
+          <t>87,34%</t>
         </is>
       </c>
     </row>
@@ -1632,57 +1632,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>237</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>167775</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>167775</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>167775</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>230</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>149551</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>149551</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>149551</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>237</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>182583</t>
+          <t>149976</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>182583</t>
+          <t>149976</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>182583</t>
+          <t>149976</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>332134</t>
+          <t>317751</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>332134</t>
+          <t>317751</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>332134</t>
+          <t>317751</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1749,57 +1749,57 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>186</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>115344</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>98906</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>144738</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>16,54%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>14,19%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>20,76%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>185</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>155395</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>123419</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>227771</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>23,46%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>18,63%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>34,39%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>186</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>135501</t>
+          <t>112087</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>115769</t>
+          <t>97094</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>168429</t>
+          <t>128435</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15,28%</t>
+          <t>15,48%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>22,23%</t>
+          <t>20,48%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>290896</t>
+          <t>227431</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>254374</t>
+          <t>204898</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>366625</t>
+          <t>257387</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>20,48%</t>
+          <t>17,17%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>17,91%</t>
+          <t>15,47%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>25,82%</t>
+          <t>19,44%</t>
         </is>
       </c>
     </row>
@@ -1862,57 +1862,57 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>783</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>581884</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>552490</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>598322</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>83,46%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>79,24%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>85,81%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>753</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>507017</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>434641</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>538993</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>76,54%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>65,61%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>81,37%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>783</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>622196</t>
+          <t>514938</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>589268</t>
+          <t>498590</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>641928</t>
+          <t>529931</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>77,77%</t>
+          <t>79,52%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>84,72%</t>
+          <t>84,52%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1129213</t>
+          <t>1096823</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1053484</t>
+          <t>1066867</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1165735</t>
+          <t>1119356</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>79,52%</t>
+          <t>82,83%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>74,18%</t>
+          <t>80,56%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>82,09%</t>
+          <t>84,53%</t>
         </is>
       </c>
     </row>
@@ -1975,57 +1975,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>969</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>697228</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>697228</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>697228</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>938</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>662412</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>662412</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>662412</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>969</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>757697</t>
+          <t>627025</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>757697</t>
+          <t>627025</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>757697</t>
+          <t>627025</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1420109</t>
+          <t>1324254</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1420109</t>
+          <t>1324254</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1420109</t>
+          <t>1324254</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
